--- a/phonenumber.xlsx
+++ b/phonenumber.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyuse\Desktop\대구한의대_소상공인\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3B457A2-888C-4ED3-9BF6-8ABBB228693B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08300BB-3787-4EE4-B624-AC4AA66520E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="600" windowWidth="9645" windowHeight="14880" xr2:uid="{1D95676F-EE95-4D74-9BC6-514A844F458F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,11 +54,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>01088068574</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01024763226</t>
+    <t>01012345678</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -473,7 +469,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -483,6 +479,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010093D531B13F7F254EB0E800C716AAD575" ma:contentTypeVersion="18" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="8bc6241ee09617a51490202a3c8a1679">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="46942688-10ae-4ea8-9fe2-c35ac173dc35" xmlns:ns4="74861016-4c27-468d-a701-0a0499d3d8e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2e3825ad10ada84cdd9b412645cbe966" ns3:_="" ns4:_="">
     <xsd:import namespace="46942688-10ae-4ea8-9fe2-c35ac173dc35"/>
@@ -735,15 +740,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -753,6 +749,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1BE8C45-CCF6-47CF-A54E-C2D788F7701B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C2F8C02-DD3B-4491-9BBB-F44348809C09}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -771,14 +775,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1BE8C45-CCF6-47CF-A54E-C2D788F7701B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A6953FB-07E6-471A-8B3A-40EED68F2F74}">
   <ds:schemaRefs>
